--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,10 +676,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>9</v>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>6</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>9</v>

--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>151</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.3642384105960265</v>
+        <v>55</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>9</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.1111111111111111</v>
+        <v>1</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K11" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>161</v>
+      </c>
+      <c r="M11" s="12" t="n">
         <v>57</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>151</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>55</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>16</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N12" headerRowCount="1">
-  <autoFilter ref="A10:N12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N13" headerRowCount="1">
+  <autoFilter ref="A10:N13"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -856,52 +856,106 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>00259</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>TETTO GARETTO</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>SCIALO' MARCO</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>00350</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>SCIALO' MARCO</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E13" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>2</v>
@@ -893,13 +893,13 @@
         <v>3</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>16</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>12</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
         <v>38</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>1</v>
@@ -896,10 +896,10 @@
         <v>15</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>16</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR SCIALO' MARCO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>3</v>
@@ -887,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J12" s="12" t="n">
         <v>3</v>
@@ -896,7 +896,7 @@
         <v>15</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>9</v>
@@ -932,7 +932,7 @@
         <v>16</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>0</v>
